--- a/data/Ljubljana_precipitation&temperature_2011-2024.xlsx
+++ b/data/Ljubljana_precipitation&temperature_2011-2024.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ijssi-my.sharepoint.com/personal/jan_gacnik_ijs_si/Documents/Jan 2023+/Voda izotopi Polona/Article Geologija/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ijssi-my.sharepoint.com/personal/jan_gacnik_ijs_si/Documents/Jan 2023+/Voda izotopi Polona/Article Geologija/Geologija_data_analysis/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="8_{869695DC-3409-4870-A687-34C20C9E4B9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E7977F8F-24DB-4D5A-86A7-6A7A25CB22C3}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="8_{869695DC-3409-4870-A687-34C20C9E4B9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{39863287-2A6E-4B84-9A3E-FB5C3D6953CB}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="1725" windowWidth="29040" windowHeight="15720" xr2:uid="{3CB29625-D1C5-4E97-B5AC-58EC43D4D069}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{3CB29625-D1C5-4E97-B5AC-58EC43D4D069}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="133">
   <si>
     <t>LJUBLJANA - REAKTOR</t>
   </si>
@@ -82,6 +82,360 @@
   </si>
   <si>
     <t>Lj - Reaktor</t>
+  </si>
+  <si>
+    <t>Hrastje</t>
+  </si>
+  <si>
+    <t>1.0  </t>
+  </si>
+  <si>
+    <t>6.5  </t>
+  </si>
+  <si>
+    <t>12.9  </t>
+  </si>
+  <si>
+    <t>16.1  </t>
+  </si>
+  <si>
+    <t>19.6  </t>
+  </si>
+  <si>
+    <t>20.7  </t>
+  </si>
+  <si>
+    <t>22.2  </t>
+  </si>
+  <si>
+    <t>19.1  </t>
+  </si>
+  <si>
+    <t>9.6  </t>
+  </si>
+  <si>
+    <t>3.6  </t>
+  </si>
+  <si>
+    <t>2.7  </t>
+  </si>
+  <si>
+    <t>0.6  </t>
+  </si>
+  <si>
+    <t>-1.9  </t>
+  </si>
+  <si>
+    <t>9.0  </t>
+  </si>
+  <si>
+    <t>10.9  </t>
+  </si>
+  <si>
+    <t>15.2  </t>
+  </si>
+  <si>
+    <t>20.4  </t>
+  </si>
+  <si>
+    <t>22.1  </t>
+  </si>
+  <si>
+    <t>22.4  </t>
+  </si>
+  <si>
+    <t>16.4  </t>
+  </si>
+  <si>
+    <t>11.2  </t>
+  </si>
+  <si>
+    <t>8.4  </t>
+  </si>
+  <si>
+    <t>0.4  </t>
+  </si>
+  <si>
+    <t>1.5  </t>
+  </si>
+  <si>
+    <t>3.5  </t>
+  </si>
+  <si>
+    <t>11.9  </t>
+  </si>
+  <si>
+    <t>14.5  </t>
+  </si>
+  <si>
+    <t>19.2  </t>
+  </si>
+  <si>
+    <t>22.8  </t>
+  </si>
+  <si>
+    <t>21.9  </t>
+  </si>
+  <si>
+    <t>15.8  </t>
+  </si>
+  <si>
+    <t>13.0  </t>
+  </si>
+  <si>
+    <t>7.1  </t>
+  </si>
+  <si>
+    <t>2.1  </t>
+  </si>
+  <si>
+    <t>5.0  </t>
+  </si>
+  <si>
+    <t>3.9  </t>
+  </si>
+  <si>
+    <t>9.2  </t>
+  </si>
+  <si>
+    <t>12.5  </t>
+  </si>
+  <si>
+    <t>15.0  </t>
+  </si>
+  <si>
+    <t>20.1  </t>
+  </si>
+  <si>
+    <t>16.0  </t>
+  </si>
+  <si>
+    <t>13.2  </t>
+  </si>
+  <si>
+    <t>8.6  </t>
+  </si>
+  <si>
+    <t>3.3  </t>
+  </si>
+  <si>
+    <t>2.2  </t>
+  </si>
+  <si>
+    <t>1.8  </t>
+  </si>
+  <si>
+    <t>6.9  </t>
+  </si>
+  <si>
+    <t>11.1  </t>
+  </si>
+  <si>
+    <t>16.3  </t>
+  </si>
+  <si>
+    <t>19.7  </t>
+  </si>
+  <si>
+    <t>23.5  </t>
+  </si>
+  <si>
+    <t>21.5  </t>
+  </si>
+  <si>
+    <t>10.7  </t>
+  </si>
+  <si>
+    <t>5.9  </t>
+  </si>
+  <si>
+    <t>1.7  </t>
+  </si>
+  <si>
+    <t>0.3  </t>
+  </si>
+  <si>
+    <t>5.1  </t>
+  </si>
+  <si>
+    <t>7.0  </t>
+  </si>
+  <si>
+    <t>11.8  </t>
+  </si>
+  <si>
+    <t>19.9  </t>
+  </si>
+  <si>
+    <t>17.4  </t>
+  </si>
+  <si>
+    <t>9.8  </t>
+  </si>
+  <si>
+    <t>6.4  </t>
+  </si>
+  <si>
+    <t>-1.1  </t>
+  </si>
+  <si>
+    <t>-4.0  </t>
+  </si>
+  <si>
+    <t>3.8  </t>
+  </si>
+  <si>
+    <t>9.5  </t>
+  </si>
+  <si>
+    <t>11.6  </t>
+  </si>
+  <si>
+    <t>21.2  </t>
+  </si>
+  <si>
+    <t>22.3  </t>
+  </si>
+  <si>
+    <t>22.6  </t>
+  </si>
+  <si>
+    <t>14.1  </t>
+  </si>
+  <si>
+    <t>5.6  </t>
+  </si>
+  <si>
+    <t>1.3  </t>
+  </si>
+  <si>
+    <t>4.3  </t>
+  </si>
+  <si>
+    <t>-0.2  </t>
+  </si>
+  <si>
+    <t>17.5  </t>
+  </si>
+  <si>
+    <t>20.3  </t>
+  </si>
+  <si>
+    <t>17.2  </t>
+  </si>
+  <si>
+    <t>12.7  </t>
+  </si>
+  <si>
+    <t>8.2  </t>
+  </si>
+  <si>
+    <t>0.0  </t>
+  </si>
+  <si>
+    <t>3.7  </t>
+  </si>
+  <si>
+    <t>12.6  </t>
+  </si>
+  <si>
+    <t>2.8  </t>
+  </si>
+  <si>
+    <t>6.2  </t>
+  </si>
+  <si>
+    <t>12.2  </t>
+  </si>
+  <si>
+    <t>14.7  </t>
+  </si>
+  <si>
+    <t>21.8  </t>
+  </si>
+  <si>
+    <t>16.9  </t>
+  </si>
+  <si>
+    <t>11.5  </t>
+  </si>
+  <si>
+    <t>4.9  </t>
+  </si>
+  <si>
+    <t>2.6  </t>
+  </si>
+  <si>
+    <t>0.9  </t>
+  </si>
+  <si>
+    <t>5.3  </t>
+  </si>
+  <si>
+    <t>8.7  </t>
+  </si>
+  <si>
+    <t>22.7  </t>
+  </si>
+  <si>
+    <t>17.0  </t>
+  </si>
+  <si>
+    <t>5.4  </t>
+  </si>
+  <si>
+    <t>0.8  </t>
+  </si>
+  <si>
+    <t>4.1  </t>
+  </si>
+  <si>
+    <t>5.7  </t>
+  </si>
+  <si>
+    <t>9.9  </t>
+  </si>
+  <si>
+    <t>22.5  </t>
+  </si>
+  <si>
+    <t>23.6  </t>
+  </si>
+  <si>
+    <t>15.7  </t>
+  </si>
+  <si>
+    <t>13.7  </t>
+  </si>
+  <si>
+    <t>7.5  </t>
+  </si>
+  <si>
+    <t>4.0  </t>
+  </si>
+  <si>
+    <t>2.5  </t>
+  </si>
+  <si>
+    <t>9.3  </t>
+  </si>
+  <si>
+    <t>19.8  </t>
+  </si>
+  <si>
+    <t>18.4  </t>
+  </si>
+  <si>
+    <t>3.4  </t>
+  </si>
+  <si>
+    <t>12.1  </t>
+  </si>
+  <si>
+    <t>15.9  </t>
+  </si>
+  <si>
+    <t>20.6  </t>
   </si>
 </sst>
 </file>
@@ -159,7 +513,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -195,6 +549,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -510,29 +870,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40FF3207-4A0E-4460-959A-D16EEA111EF5}">
-  <dimension ref="A1:K173"/>
+  <dimension ref="A1:L173"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="4"/>
     <col min="2" max="2" width="13.796875" style="4" customWidth="1"/>
     <col min="3" max="3" width="17.19921875" style="12" customWidth="1"/>
-    <col min="4" max="4" width="13.8984375" style="12" customWidth="1"/>
-    <col min="5" max="10" width="9" style="4"/>
+    <col min="4" max="5" width="13.8984375" style="12" customWidth="1"/>
+    <col min="6" max="11" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="6"/>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B2" s="6"/>
     </row>
-    <row r="3" spans="1:11" ht="53.4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" ht="53.4" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
         <v>1</v>
       </c>
@@ -545,27 +905,30 @@
       <c r="D3" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="18" t="s">
+      <c r="E3" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="G3" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="19" t="s">
+      <c r="H3" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="19" t="s">
+      <c r="I3" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="19" t="s">
+      <c r="J3" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="J3" s="19" t="s">
+      <c r="K3" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="2"/>
-    </row>
-    <row r="4" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L3" s="2"/>
+    </row>
+    <row r="4" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5"/>
       <c r="B4" s="9" t="s">
         <v>4</v>
@@ -576,9 +939,12 @@
       <c r="D4" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="K4" s="2"/>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="E4" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="L4" s="2"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="7"/>
       <c r="B5" s="9" t="s">
         <v>14</v>
@@ -589,15 +955,18 @@
       <c r="D5" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="7"/>
+      <c r="E5" s="13" t="s">
+        <v>15</v>
+      </c>
       <c r="F5" s="7"/>
       <c r="G5" s="7"/>
       <c r="H5" s="7"/>
       <c r="I5" s="7"/>
       <c r="J5" s="7"/>
-      <c r="K5" s="1"/>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K5" s="7"/>
+      <c r="L5" s="1"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="10">
         <v>40544</v>
       </c>
@@ -610,8 +979,11 @@
       <c r="D6" s="12">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="E6" s="20" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="10">
         <v>40575</v>
       </c>
@@ -624,8 +996,11 @@
       <c r="D7" s="12">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="E7" s="20" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="10">
         <v>40603</v>
       </c>
@@ -638,8 +1013,11 @@
       <c r="D8" s="12">
         <v>7.1</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="E8" s="20" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="10">
         <v>40634</v>
       </c>
@@ -652,8 +1030,11 @@
       <c r="D9" s="12">
         <v>13.5</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="E9" s="20" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="10">
         <v>40664</v>
       </c>
@@ -666,8 +1047,11 @@
       <c r="D10" s="12">
         <v>17</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="E10" s="20" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="10">
         <v>40695</v>
       </c>
@@ -680,8 +1064,11 @@
       <c r="D11" s="12">
         <v>20</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="E11" s="20" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="10">
         <v>40725</v>
       </c>
@@ -694,8 +1081,11 @@
       <c r="D12" s="12">
         <v>21.1</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="E12" s="20" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="10">
         <v>40756</v>
       </c>
@@ -708,8 +1098,11 @@
       <c r="D13" s="12">
         <v>22.8</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="E13" s="20" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="10">
         <v>40787</v>
       </c>
@@ -722,8 +1115,11 @@
       <c r="D14" s="12">
         <v>19.399999999999999</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="E14" s="20" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="10">
         <v>40817</v>
       </c>
@@ -736,8 +1132,11 @@
       <c r="D15" s="12">
         <v>10</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="E15" s="20" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="10">
         <v>40848</v>
       </c>
@@ -750,8 +1149,11 @@
       <c r="D16" s="12">
         <v>3.8</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E16" s="20" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="10">
         <v>40878</v>
       </c>
@@ -764,8 +1166,11 @@
       <c r="D17" s="12">
         <v>3.3</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E17" s="20" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="10">
         <v>40909</v>
       </c>
@@ -778,8 +1183,11 @@
       <c r="D18" s="12">
         <v>1.6</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E18" s="20" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="10">
         <v>40940</v>
       </c>
@@ -792,8 +1200,11 @@
       <c r="D19" s="12">
         <v>-0.8</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E19" s="20" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="10">
         <v>40969</v>
       </c>
@@ -806,8 +1217,11 @@
       <c r="D20" s="12">
         <v>10.1</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E20" s="20" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="10">
         <v>41000</v>
       </c>
@@ -820,8 +1234,11 @@
       <c r="D21" s="12">
         <v>11.4</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E21" s="20" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="10">
         <v>41030</v>
       </c>
@@ -834,8 +1251,11 @@
       <c r="D22" s="12">
         <v>16.100000000000001</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E22" s="20" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="10">
         <v>41061</v>
       </c>
@@ -848,8 +1268,11 @@
       <c r="D23" s="12">
         <v>21.3</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E23" s="20" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="10">
         <v>41091</v>
       </c>
@@ -862,8 +1285,11 @@
       <c r="D24" s="12">
         <v>22.7</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E24" s="20" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="10">
         <v>41122</v>
       </c>
@@ -876,8 +1302,11 @@
       <c r="D25" s="12">
         <v>23.3</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E25" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
         <v>41153</v>
       </c>
@@ -890,8 +1319,11 @@
       <c r="D26" s="12">
         <v>17</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E26" s="20" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="10">
         <v>41183</v>
       </c>
@@ -904,8 +1336,11 @@
       <c r="D27" s="12">
         <v>11.7</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E27" s="20" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="10">
         <v>41214</v>
       </c>
@@ -918,8 +1353,11 @@
       <c r="D28" s="12">
         <v>8.8000000000000007</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E28" s="20" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="10">
         <v>41244</v>
       </c>
@@ -932,8 +1370,11 @@
       <c r="D29" s="12">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E29" s="20" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
         <v>41275</v>
       </c>
@@ -946,8 +1387,11 @@
       <c r="D30" s="14">
         <v>2</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E30" s="21" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="10">
         <v>41306</v>
       </c>
@@ -960,8 +1404,11 @@
       <c r="D31" s="14">
         <v>0.9</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E31" s="21" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="10">
         <v>41334</v>
       </c>
@@ -974,8 +1421,11 @@
       <c r="D32" s="14">
         <v>3.9</v>
       </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E32" s="21" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" s="10">
         <v>41365</v>
       </c>
@@ -988,8 +1438,11 @@
       <c r="D33" s="14">
         <v>12.4</v>
       </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E33" s="21" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" s="10">
         <v>41395</v>
       </c>
@@ -1002,8 +1455,11 @@
       <c r="D34" s="14">
         <v>14.8</v>
       </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E34" s="21" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" s="10">
         <v>41426</v>
       </c>
@@ -1016,8 +1472,11 @@
       <c r="D35" s="14">
         <v>19.8</v>
       </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E35" s="21" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" s="10">
         <v>41456</v>
       </c>
@@ -1030,8 +1489,11 @@
       <c r="D36" s="14">
         <v>23.5</v>
       </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E36" s="21" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" s="10">
         <v>41487</v>
       </c>
@@ -1044,8 +1506,11 @@
       <c r="D37" s="14">
         <v>22.5</v>
       </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E37" s="21" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
         <v>41518</v>
       </c>
@@ -1058,8 +1523,11 @@
       <c r="D38" s="14">
         <v>16.2</v>
       </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E38" s="21" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" s="10">
         <v>41548</v>
       </c>
@@ -1072,8 +1540,11 @@
       <c r="D39" s="14">
         <v>13.2</v>
       </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E39" s="21" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" s="10">
         <v>41579</v>
       </c>
@@ -1086,8 +1557,11 @@
       <c r="D40" s="14">
         <v>7.3</v>
       </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E40" s="21" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" s="10">
         <v>41609</v>
       </c>
@@ -1100,8 +1574,11 @@
       <c r="D41" s="14">
         <v>2.7</v>
       </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E41" s="21" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" s="10">
         <v>41640</v>
       </c>
@@ -1114,24 +1591,27 @@
       <c r="D42" s="14">
         <v>5.4</v>
       </c>
-      <c r="E42" s="4">
+      <c r="E42" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="F42" s="4">
         <v>90</v>
       </c>
-      <c r="F42" s="4">
+      <c r="G42" s="4">
         <v>17</v>
       </c>
-      <c r="G42" s="4">
+      <c r="H42" s="4">
         <v>14</v>
       </c>
-      <c r="H42" s="4">
+      <c r="I42" s="4">
         <v>2</v>
       </c>
-      <c r="I42" s="4">
+      <c r="J42" s="4">
         <v>6</v>
       </c>
-      <c r="J42" s="16"/>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K42" s="16"/>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" s="10">
         <v>41671</v>
       </c>
@@ -1144,24 +1624,27 @@
       <c r="D43" s="14">
         <v>4.4000000000000004</v>
       </c>
-      <c r="E43" s="4">
+      <c r="E43" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="F43" s="4">
         <v>88</v>
-      </c>
-      <c r="F43" s="4">
-        <v>21</v>
       </c>
       <c r="G43" s="4">
         <v>21</v>
       </c>
       <c r="H43" s="4">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="I43" s="4">
         <v>6</v>
       </c>
-      <c r="J43" s="12"/>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J43" s="4">
+        <v>6</v>
+      </c>
+      <c r="K43" s="12"/>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" s="10">
         <v>41699</v>
       </c>
@@ -1174,24 +1657,27 @@
       <c r="D44" s="14">
         <v>10</v>
       </c>
-      <c r="E44" s="4">
+      <c r="E44" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="F44" s="4">
         <v>67</v>
-      </c>
-      <c r="F44" s="4">
-        <v>9</v>
       </c>
       <c r="G44" s="4">
         <v>9</v>
       </c>
       <c r="H44" s="4">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I44" s="4">
         <v>0</v>
       </c>
-      <c r="J44" s="12"/>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J44" s="4">
+        <v>0</v>
+      </c>
+      <c r="K44" s="12"/>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" s="10">
         <v>41730</v>
       </c>
@@ -1204,24 +1690,27 @@
       <c r="D45" s="14">
         <v>13.1</v>
       </c>
-      <c r="E45" s="4">
+      <c r="E45" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="F45" s="4">
         <v>72</v>
-      </c>
-      <c r="F45" s="4">
-        <v>14</v>
       </c>
       <c r="G45" s="4">
         <v>14</v>
       </c>
       <c r="H45" s="4">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I45" s="4">
         <v>0</v>
       </c>
-      <c r="J45" s="12"/>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J45" s="4">
+        <v>0</v>
+      </c>
+      <c r="K45" s="12"/>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" s="10">
         <v>41760</v>
       </c>
@@ -1234,24 +1723,27 @@
       <c r="D46" s="14">
         <v>15.7</v>
       </c>
-      <c r="E46" s="4">
+      <c r="E46" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="F46" s="4">
         <v>65</v>
-      </c>
-      <c r="F46" s="4">
-        <v>15</v>
       </c>
       <c r="G46" s="4">
         <v>15</v>
       </c>
       <c r="H46" s="4">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I46" s="4">
         <v>0</v>
       </c>
-      <c r="J46" s="12"/>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J46" s="4">
+        <v>0</v>
+      </c>
+      <c r="K46" s="12"/>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" s="10">
         <v>41791</v>
       </c>
@@ -1264,24 +1756,27 @@
       <c r="D47" s="14">
         <v>20.2</v>
       </c>
-      <c r="E47" s="4">
+      <c r="E47" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="F47" s="4">
         <v>66</v>
-      </c>
-      <c r="F47" s="4">
-        <v>14</v>
       </c>
       <c r="G47" s="4">
         <v>14</v>
       </c>
       <c r="H47" s="4">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I47" s="4">
         <v>0</v>
       </c>
-      <c r="J47" s="12"/>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J47" s="4">
+        <v>0</v>
+      </c>
+      <c r="K47" s="12"/>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" s="10">
         <v>41821</v>
       </c>
@@ -1294,24 +1789,27 @@
       <c r="D48" s="14">
         <v>20.8</v>
       </c>
-      <c r="E48" s="4">
+      <c r="E48" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="F48" s="4">
         <v>75</v>
-      </c>
-      <c r="F48" s="4">
-        <v>21</v>
       </c>
       <c r="G48" s="4">
         <v>21</v>
       </c>
       <c r="H48" s="4">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="I48" s="4">
         <v>0</v>
       </c>
-      <c r="J48" s="12"/>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J48" s="4">
+        <v>0</v>
+      </c>
+      <c r="K48" s="12"/>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49" s="10">
         <v>41852</v>
       </c>
@@ -1324,24 +1822,27 @@
       <c r="D49" s="14">
         <v>19.600000000000001</v>
       </c>
-      <c r="E49" s="4">
+      <c r="E49" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="F49" s="4">
         <v>76</v>
-      </c>
-      <c r="F49" s="4">
-        <v>14</v>
       </c>
       <c r="G49" s="4">
         <v>14</v>
       </c>
       <c r="H49" s="4">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I49" s="4">
         <v>0</v>
       </c>
-      <c r="J49" s="12"/>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J49" s="4">
+        <v>0</v>
+      </c>
+      <c r="K49" s="12"/>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" s="10">
         <v>41883</v>
       </c>
@@ -1354,24 +1855,27 @@
       <c r="D50" s="14">
         <v>16.2</v>
       </c>
-      <c r="E50" s="4">
+      <c r="E50" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="F50" s="4">
         <v>83</v>
-      </c>
-      <c r="F50" s="4">
-        <v>17</v>
       </c>
       <c r="G50" s="4">
         <v>17</v>
       </c>
       <c r="H50" s="4">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="I50" s="4">
         <v>0</v>
       </c>
-      <c r="J50" s="12"/>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J50" s="4">
+        <v>0</v>
+      </c>
+      <c r="K50" s="12"/>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51" s="10">
         <v>41913</v>
       </c>
@@ -1384,24 +1888,27 @@
       <c r="D51" s="14">
         <v>13.6</v>
       </c>
-      <c r="E51" s="4">
+      <c r="E51" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="F51" s="4">
         <v>81</v>
-      </c>
-      <c r="F51" s="4">
-        <v>11</v>
       </c>
       <c r="G51" s="4">
         <v>11</v>
       </c>
       <c r="H51" s="4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I51" s="4">
         <v>0</v>
       </c>
-      <c r="J51" s="12"/>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J51" s="4">
+        <v>0</v>
+      </c>
+      <c r="K51" s="12"/>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52" s="10">
         <v>41944</v>
       </c>
@@ -1414,24 +1921,27 @@
       <c r="D52" s="14">
         <v>8.8000000000000007</v>
       </c>
-      <c r="E52" s="4">
+      <c r="E52" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="F52" s="4">
         <v>92</v>
-      </c>
-      <c r="F52" s="4">
-        <v>21</v>
       </c>
       <c r="G52" s="4">
         <v>21</v>
       </c>
       <c r="H52" s="4">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="I52" s="4">
         <v>0</v>
       </c>
-      <c r="J52" s="12"/>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J52" s="4">
+        <v>0</v>
+      </c>
+      <c r="K52" s="12"/>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53" s="10">
         <v>41974</v>
       </c>
@@ -1444,24 +1954,27 @@
       <c r="D53" s="14">
         <v>3.9</v>
       </c>
-      <c r="E53" s="4">
+      <c r="E53" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="F53" s="4">
         <v>84</v>
       </c>
-      <c r="F53" s="4">
+      <c r="G53" s="4">
         <v>15</v>
       </c>
-      <c r="G53" s="4">
+      <c r="H53" s="4">
         <v>13</v>
-      </c>
-      <c r="H53" s="4">
-        <v>2</v>
       </c>
       <c r="I53" s="4">
         <v>2</v>
       </c>
-      <c r="J53" s="12"/>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J53" s="4">
+        <v>2</v>
+      </c>
+      <c r="K53" s="12"/>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54" s="10">
         <v>42005</v>
       </c>
@@ -1474,24 +1987,27 @@
       <c r="D54" s="12">
         <v>2.8</v>
       </c>
-      <c r="E54" s="4">
+      <c r="E54" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="F54" s="4">
         <v>83</v>
-      </c>
-      <c r="F54" s="4">
-        <v>11</v>
       </c>
       <c r="G54" s="4">
         <v>11</v>
       </c>
       <c r="H54" s="4">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="I54" s="4">
         <v>2</v>
       </c>
-      <c r="J54" s="12"/>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J54" s="4">
+        <v>2</v>
+      </c>
+      <c r="K54" s="12"/>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55" s="10">
         <v>42036</v>
       </c>
@@ -1504,24 +2020,27 @@
       <c r="D55" s="12">
         <v>2.4</v>
       </c>
-      <c r="E55" s="4">
+      <c r="E55" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="F55" s="4">
         <v>82</v>
       </c>
-      <c r="F55" s="4">
+      <c r="G55" s="4">
         <v>12</v>
       </c>
-      <c r="G55" s="4">
+      <c r="H55" s="4">
         <v>6</v>
       </c>
-      <c r="H55" s="4">
-        <v>0</v>
-      </c>
       <c r="I55" s="4">
+        <v>0</v>
+      </c>
+      <c r="J55" s="4">
         <v>6</v>
       </c>
-      <c r="J55" s="12"/>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K55" s="12"/>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56" s="10">
         <v>42064</v>
       </c>
@@ -1534,24 +2053,27 @@
       <c r="D56" s="12">
         <v>7.6</v>
       </c>
-      <c r="E56" s="4">
+      <c r="E56" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="F56" s="4">
         <v>68</v>
-      </c>
-      <c r="F56" s="4">
-        <v>9</v>
       </c>
       <c r="G56" s="4">
         <v>9</v>
       </c>
       <c r="H56" s="4">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I56" s="4">
         <v>0</v>
       </c>
-      <c r="J56" s="16"/>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J56" s="4">
+        <v>0</v>
+      </c>
+      <c r="K56" s="16"/>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57" s="10">
         <v>42095</v>
       </c>
@@ -1564,24 +2086,27 @@
       <c r="D57" s="12">
         <v>11.8</v>
       </c>
-      <c r="E57" s="4">
+      <c r="E57" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="F57" s="4">
         <v>62</v>
-      </c>
-      <c r="F57" s="4">
-        <v>8</v>
       </c>
       <c r="G57" s="4">
         <v>8</v>
       </c>
       <c r="H57" s="4">
+        <v>8</v>
+      </c>
+      <c r="I57" s="4">
         <v>1</v>
       </c>
-      <c r="I57" s="4">
-        <v>0</v>
-      </c>
-      <c r="J57" s="12"/>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J57" s="4">
+        <v>0</v>
+      </c>
+      <c r="K57" s="12"/>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58" s="10">
         <v>42125</v>
       </c>
@@ -1594,23 +2119,26 @@
       <c r="D58" s="12">
         <v>17</v>
       </c>
-      <c r="E58" s="4">
+      <c r="E58" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="F58" s="4">
         <v>70</v>
-      </c>
-      <c r="F58" s="4">
-        <v>12</v>
       </c>
       <c r="G58" s="4">
         <v>12</v>
       </c>
       <c r="H58" s="4">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I58" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J58" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59" s="10">
         <v>42156</v>
       </c>
@@ -1623,23 +2151,26 @@
       <c r="D59" s="12">
         <v>20.6</v>
       </c>
-      <c r="E59" s="4">
+      <c r="E59" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="F59" s="4">
         <v>66</v>
-      </c>
-      <c r="F59" s="4">
-        <v>10</v>
       </c>
       <c r="G59" s="4">
         <v>10</v>
       </c>
       <c r="H59" s="4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I59" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J59" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60" s="10">
         <v>42186</v>
       </c>
@@ -1652,23 +2183,26 @@
       <c r="D60" s="12">
         <v>24.3</v>
       </c>
-      <c r="E60" s="4">
+      <c r="E60" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="F60" s="4">
         <v>67</v>
-      </c>
-      <c r="F60" s="4">
-        <v>10</v>
       </c>
       <c r="G60" s="4">
         <v>10</v>
       </c>
       <c r="H60" s="4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I60" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J60" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A61" s="10">
         <v>42217</v>
       </c>
@@ -1681,23 +2215,26 @@
       <c r="D61" s="12">
         <v>22.3</v>
       </c>
-      <c r="E61" s="4">
+      <c r="E61" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="F61" s="4">
         <v>72</v>
-      </c>
-      <c r="F61" s="4">
-        <v>11</v>
       </c>
       <c r="G61" s="4">
         <v>11</v>
       </c>
       <c r="H61" s="4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I61" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J61" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A62" s="10">
         <v>42248</v>
       </c>
@@ -1710,23 +2247,26 @@
       <c r="D62" s="12">
         <v>16.5</v>
       </c>
-      <c r="E62" s="4">
+      <c r="E62" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="F62" s="4">
         <v>76</v>
-      </c>
-      <c r="F62" s="4">
-        <v>12</v>
       </c>
       <c r="G62" s="4">
         <v>12</v>
       </c>
       <c r="H62" s="4">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I62" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J62" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A63" s="10">
         <v>42278</v>
       </c>
@@ -1739,23 +2279,26 @@
       <c r="D63" s="12">
         <v>11</v>
       </c>
-      <c r="E63" s="4">
+      <c r="E63" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="F63" s="4">
         <v>86</v>
-      </c>
-      <c r="F63" s="4">
-        <v>17</v>
       </c>
       <c r="G63" s="4">
         <v>17</v>
       </c>
       <c r="H63" s="4">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="I63" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J63" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A64" s="10">
         <v>42309</v>
       </c>
@@ -1768,23 +2311,26 @@
       <c r="D64" s="12">
         <v>6.9</v>
       </c>
-      <c r="E64" s="4">
+      <c r="E64" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="F64" s="4">
         <v>82</v>
-      </c>
-      <c r="F64" s="4">
-        <v>5</v>
       </c>
       <c r="G64" s="4">
         <v>5</v>
       </c>
       <c r="H64" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I64" s="4">
         <v>3</v>
       </c>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J64" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" s="10">
         <v>42339</v>
       </c>
@@ -1797,23 +2343,26 @@
       <c r="D65" s="12">
         <v>2.6</v>
       </c>
-      <c r="E65" s="4">
+      <c r="E65" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="F65" s="4">
         <v>92</v>
-      </c>
-      <c r="F65" s="4">
-        <v>5</v>
       </c>
       <c r="G65" s="4">
         <v>5</v>
       </c>
       <c r="H65" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I65" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J65" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" s="10">
         <v>42370</v>
       </c>
@@ -1826,23 +2375,26 @@
       <c r="D66" s="12">
         <v>1.1000000000000001</v>
       </c>
-      <c r="E66" s="4">
+      <c r="E66" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="F66" s="4">
         <v>85</v>
       </c>
-      <c r="F66" s="4">
+      <c r="G66" s="4">
         <v>12</v>
       </c>
-      <c r="G66" s="4">
+      <c r="H66" s="4">
         <v>10</v>
       </c>
-      <c r="H66" s="4">
+      <c r="I66" s="4">
         <v>1</v>
       </c>
-      <c r="I66" s="4">
+      <c r="J66" s="4">
         <v>6</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" s="10">
         <v>42401</v>
       </c>
@@ -1855,23 +2407,26 @@
       <c r="D67" s="12">
         <v>5.5</v>
       </c>
-      <c r="E67" s="4">
+      <c r="E67" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="F67" s="4">
         <v>86</v>
-      </c>
-      <c r="F67" s="4">
-        <v>20</v>
       </c>
       <c r="G67" s="4">
         <v>20</v>
       </c>
       <c r="H67" s="4">
+        <v>20</v>
+      </c>
+      <c r="I67" s="4">
         <v>9</v>
       </c>
-      <c r="I67" s="4">
+      <c r="J67" s="4">
         <v>4</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" s="10">
         <v>42430</v>
       </c>
@@ -1884,23 +2439,26 @@
       <c r="D68" s="12">
         <v>7.5</v>
       </c>
-      <c r="E68" s="4">
+      <c r="E68" s="20" t="s">
         <v>73</v>
       </c>
       <c r="F68" s="4">
-        <v>13</v>
+        <v>73</v>
       </c>
       <c r="G68" s="4">
         <v>13</v>
       </c>
       <c r="H68" s="4">
+        <v>13</v>
+      </c>
+      <c r="I68" s="4">
         <v>3</v>
       </c>
-      <c r="I68" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J68" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" s="10">
         <v>42461</v>
       </c>
@@ -1913,23 +2471,26 @@
       <c r="D69" s="12">
         <v>12.5</v>
       </c>
-      <c r="E69" s="4">
+      <c r="E69" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="F69" s="4">
         <v>70</v>
-      </c>
-      <c r="F69" s="4">
-        <v>11</v>
       </c>
       <c r="G69" s="4">
         <v>11</v>
       </c>
       <c r="H69" s="4">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="I69" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J69" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" s="10">
         <v>42491</v>
       </c>
@@ -1942,23 +2503,26 @@
       <c r="D70" s="12">
         <v>15.3</v>
       </c>
-      <c r="E70" s="4">
+      <c r="E70" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="F70" s="4">
         <v>71</v>
-      </c>
-      <c r="F70" s="4">
-        <v>19</v>
       </c>
       <c r="G70" s="4">
         <v>19</v>
       </c>
       <c r="H70" s="4">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="I70" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J70" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" s="10">
         <v>42522</v>
       </c>
@@ -1971,23 +2535,26 @@
       <c r="D71" s="12">
         <v>20</v>
       </c>
-      <c r="E71" s="4">
+      <c r="E71" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="F71" s="4">
         <v>73</v>
-      </c>
-      <c r="F71" s="4">
-        <v>19</v>
       </c>
       <c r="G71" s="4">
         <v>19</v>
       </c>
       <c r="H71" s="4">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="I71" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J71" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" s="10">
         <v>42552</v>
       </c>
@@ -2000,23 +2567,26 @@
       <c r="D72" s="12">
         <v>23.2</v>
       </c>
-      <c r="E72" s="4">
+      <c r="E72" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F72" s="4">
         <v>67</v>
-      </c>
-      <c r="F72" s="4">
-        <v>12</v>
       </c>
       <c r="G72" s="4">
         <v>12</v>
       </c>
       <c r="H72" s="4">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I72" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J72" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" s="10">
         <v>42583</v>
       </c>
@@ -2029,23 +2599,26 @@
       <c r="D73" s="12">
         <v>20.6</v>
       </c>
-      <c r="E73" s="4">
+      <c r="E73" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="F73" s="4">
         <v>71</v>
-      </c>
-      <c r="F73" s="4">
-        <v>10</v>
       </c>
       <c r="G73" s="4">
         <v>10</v>
       </c>
       <c r="H73" s="4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I73" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J73" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" s="10">
         <v>42614</v>
       </c>
@@ -2058,23 +2631,26 @@
       <c r="D74" s="12">
         <v>18.3</v>
       </c>
-      <c r="E74" s="4">
+      <c r="E74" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="F74" s="4">
         <v>74</v>
-      </c>
-      <c r="F74" s="4">
-        <v>10</v>
       </c>
       <c r="G74" s="4">
         <v>10</v>
       </c>
       <c r="H74" s="4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I74" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J74" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" s="10">
         <v>42644</v>
       </c>
@@ -2087,23 +2663,26 @@
       <c r="D75" s="12">
         <v>10.3</v>
       </c>
-      <c r="E75" s="4">
+      <c r="E75" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="F75" s="4">
         <v>85</v>
-      </c>
-      <c r="F75" s="4">
-        <v>16</v>
       </c>
       <c r="G75" s="4">
         <v>16</v>
       </c>
       <c r="H75" s="4">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I75" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J75" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76" s="10">
         <v>42675</v>
       </c>
@@ -2116,23 +2695,26 @@
       <c r="D76" s="12">
         <v>7</v>
       </c>
-      <c r="E76" s="4">
+      <c r="E76" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="F76" s="4">
         <v>84</v>
       </c>
-      <c r="F76" s="4">
+      <c r="G76" s="4">
         <v>22</v>
       </c>
-      <c r="G76" s="4">
+      <c r="H76" s="4">
         <v>21</v>
       </c>
-      <c r="H76" s="4">
-        <v>0</v>
-      </c>
       <c r="I76" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J76" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A77" s="10">
         <v>42705</v>
       </c>
@@ -2145,23 +2727,26 @@
       <c r="D77" s="12">
         <v>-0.2</v>
       </c>
-      <c r="E77" s="4">
+      <c r="E77" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="F77" s="4">
         <v>84</v>
       </c>
-      <c r="F77" s="4">
+      <c r="G77" s="4">
         <v>1</v>
       </c>
-      <c r="G77" s="4">
-        <v>0</v>
-      </c>
       <c r="H77" s="4">
         <v>0</v>
       </c>
       <c r="I77" s="4">
+        <v>0</v>
+      </c>
+      <c r="J77" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78" s="10">
         <v>42736</v>
       </c>
@@ -2174,23 +2759,26 @@
       <c r="D78" s="12">
         <v>-3.2</v>
       </c>
-      <c r="E78" s="4">
+      <c r="E78" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="F78" s="4">
         <v>78</v>
       </c>
-      <c r="F78" s="4">
+      <c r="G78" s="4">
         <v>4</v>
       </c>
-      <c r="G78" s="4">
+      <c r="H78" s="4">
         <v>3</v>
       </c>
-      <c r="H78" s="4">
+      <c r="I78" s="4">
         <v>2</v>
       </c>
-      <c r="I78" s="4">
+      <c r="J78" s="4">
         <v>4</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" s="10">
         <v>42767</v>
       </c>
@@ -2203,23 +2791,26 @@
       <c r="D79" s="12">
         <v>4.5</v>
       </c>
-      <c r="E79" s="4">
+      <c r="E79" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="F79" s="4">
         <v>82</v>
-      </c>
-      <c r="F79" s="4">
-        <v>12</v>
       </c>
       <c r="G79" s="4">
         <v>12</v>
       </c>
       <c r="H79" s="4">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="I79" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J79" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" s="10">
         <v>42795</v>
       </c>
@@ -2232,23 +2823,26 @@
       <c r="D80" s="12">
         <v>10.199999999999999</v>
       </c>
-      <c r="E80" s="4">
+      <c r="E80" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="F80" s="4">
         <v>66</v>
-      </c>
-      <c r="F80" s="4">
-        <v>5</v>
       </c>
       <c r="G80" s="4">
         <v>5</v>
       </c>
       <c r="H80" s="4">
+        <v>5</v>
+      </c>
+      <c r="I80" s="4">
         <v>2</v>
       </c>
-      <c r="I80" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J80" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" s="10">
         <v>42826</v>
       </c>
@@ -2261,23 +2855,26 @@
       <c r="D81" s="12">
         <v>12.1</v>
       </c>
-      <c r="E81" s="4">
+      <c r="E81" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="F81" s="4">
         <v>66</v>
-      </c>
-      <c r="F81" s="4">
-        <v>12</v>
       </c>
       <c r="G81" s="4">
         <v>12</v>
       </c>
       <c r="H81" s="4">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I81" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J81" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A82" s="10">
         <v>42856</v>
       </c>
@@ -2290,23 +2887,26 @@
       <c r="D82" s="12">
         <v>16.899999999999999</v>
       </c>
-      <c r="E82" s="4">
+      <c r="E82" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="F82" s="4">
         <v>68</v>
-      </c>
-      <c r="F82" s="4">
-        <v>15</v>
       </c>
       <c r="G82" s="4">
         <v>15</v>
       </c>
       <c r="H82" s="4">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I82" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J82" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A83" s="10">
         <v>42887</v>
       </c>
@@ -2319,23 +2919,26 @@
       <c r="D83" s="12">
         <v>21.7</v>
       </c>
-      <c r="E83" s="4">
+      <c r="E83" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="F83" s="4">
         <v>66</v>
-      </c>
-      <c r="F83" s="4">
-        <v>10</v>
       </c>
       <c r="G83" s="4">
         <v>10</v>
       </c>
       <c r="H83" s="4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I83" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J83" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A84" s="10">
         <v>42917</v>
       </c>
@@ -2348,23 +2951,26 @@
       <c r="D84" s="12">
         <v>23.2</v>
       </c>
-      <c r="E84" s="4">
+      <c r="E84" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="F84" s="4">
         <v>62</v>
-      </c>
-      <c r="F84" s="4">
-        <v>10</v>
       </c>
       <c r="G84" s="4">
         <v>10</v>
       </c>
       <c r="H84" s="4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I84" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J84" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A85" s="10">
         <v>42948</v>
       </c>
@@ -2377,23 +2983,26 @@
       <c r="D85" s="12">
         <v>23.2</v>
       </c>
-      <c r="E85" s="4">
+      <c r="E85" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="F85" s="4">
         <v>65</v>
-      </c>
-      <c r="F85" s="4">
-        <v>8</v>
       </c>
       <c r="G85" s="4">
         <v>8</v>
       </c>
       <c r="H85" s="4">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I85" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J85" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A86" s="10">
         <v>42979</v>
       </c>
@@ -2406,23 +3015,26 @@
       <c r="D86" s="12">
         <v>14.3</v>
       </c>
-      <c r="E86" s="4">
+      <c r="E86" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="F86" s="4">
         <v>84</v>
-      </c>
-      <c r="F86" s="4">
-        <v>17</v>
       </c>
       <c r="G86" s="4">
         <v>17</v>
       </c>
       <c r="H86" s="4">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="I86" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J86" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A87" s="10">
         <v>43009</v>
       </c>
@@ -2435,23 +3047,26 @@
       <c r="D87" s="12">
         <v>12</v>
       </c>
-      <c r="E87" s="4">
+      <c r="E87" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="F87" s="4">
         <v>75</v>
       </c>
-      <c r="F87" s="4">
+      <c r="G87" s="4">
         <v>8</v>
       </c>
-      <c r="G87" s="4">
+      <c r="H87" s="4">
         <v>7</v>
       </c>
-      <c r="H87" s="4">
-        <v>0</v>
-      </c>
       <c r="I87" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J87" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A88" s="10">
         <v>43040</v>
       </c>
@@ -2464,23 +3079,26 @@
       <c r="D88" s="12">
         <v>6.2</v>
       </c>
-      <c r="E88" s="4">
+      <c r="E88" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="F88" s="4">
         <v>84</v>
-      </c>
-      <c r="F88" s="4">
-        <v>10</v>
       </c>
       <c r="G88" s="4">
         <v>10</v>
       </c>
       <c r="H88" s="4">
+        <v>10</v>
+      </c>
+      <c r="I88" s="4">
         <v>5</v>
       </c>
-      <c r="I88" s="4">
+      <c r="J88" s="4">
         <v>3</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A89" s="10">
         <v>43070</v>
       </c>
@@ -2493,23 +3111,26 @@
       <c r="D89" s="12">
         <v>1.9</v>
       </c>
-      <c r="E89" s="4">
+      <c r="E89" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="F89" s="4">
         <v>91</v>
-      </c>
-      <c r="F89" s="4">
-        <v>14</v>
       </c>
       <c r="G89" s="4">
         <v>14</v>
       </c>
       <c r="H89" s="4">
+        <v>14</v>
+      </c>
+      <c r="I89" s="4">
         <v>7</v>
       </c>
-      <c r="I89" s="4">
+      <c r="J89" s="4">
         <v>9</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A90" s="10">
         <v>43101</v>
       </c>
@@ -2522,23 +3143,26 @@
       <c r="D90" s="12">
         <v>4.8</v>
       </c>
-      <c r="E90" s="4">
+      <c r="E90" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="F90" s="4">
         <v>85</v>
       </c>
-      <c r="F90" s="4">
+      <c r="G90" s="4">
         <v>14</v>
       </c>
-      <c r="G90" s="4">
+      <c r="H90" s="4">
         <v>13</v>
-      </c>
-      <c r="H90" s="4">
-        <v>2</v>
       </c>
       <c r="I90" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J90" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A91" s="10">
         <v>43132</v>
       </c>
@@ -2551,23 +3175,26 @@
       <c r="D91" s="12">
         <v>-0.1</v>
       </c>
-      <c r="E91" s="4">
+      <c r="E91" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="F91" s="4">
         <v>82</v>
       </c>
-      <c r="F91" s="4">
+      <c r="G91" s="4">
         <v>14</v>
       </c>
-      <c r="G91" s="4">
+      <c r="H91" s="4">
         <v>5</v>
       </c>
-      <c r="H91" s="4">
+      <c r="I91" s="4">
         <v>4</v>
       </c>
-      <c r="I91" s="4">
+      <c r="J91" s="4">
         <v>12</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A92" s="10">
         <v>43160</v>
       </c>
@@ -2580,23 +3207,26 @@
       <c r="D92" s="12">
         <v>4.5999999999999996</v>
       </c>
-      <c r="E92" s="4">
+      <c r="E92" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="F92" s="4">
         <v>78</v>
       </c>
-      <c r="F92" s="4">
+      <c r="G92" s="4">
         <v>19</v>
       </c>
-      <c r="G92" s="4">
+      <c r="H92" s="4">
         <v>18</v>
       </c>
-      <c r="H92" s="4">
-        <v>0</v>
-      </c>
       <c r="I92" s="4">
+        <v>0</v>
+      </c>
+      <c r="J92" s="4">
         <v>7</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A93" s="10">
         <v>43191</v>
       </c>
@@ -2609,23 +3239,26 @@
       <c r="D93" s="12">
         <v>15.2</v>
       </c>
-      <c r="E93" s="4">
+      <c r="E93" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="F93" s="4">
         <v>65</v>
-      </c>
-      <c r="F93" s="4">
-        <v>12</v>
       </c>
       <c r="G93" s="4">
         <v>12</v>
       </c>
       <c r="H93" s="4">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I93" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J93" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A94" s="10">
         <v>43221</v>
       </c>
@@ -2638,23 +3271,26 @@
       <c r="D94" s="12">
         <v>18</v>
       </c>
-      <c r="E94" s="4">
+      <c r="E94" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="F94" s="4">
         <v>75</v>
-      </c>
-      <c r="F94" s="4">
-        <v>15</v>
       </c>
       <c r="G94" s="4">
         <v>15</v>
       </c>
       <c r="H94" s="4">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I94" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J94" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A95" s="10">
         <v>43252</v>
       </c>
@@ -2667,23 +3303,26 @@
       <c r="D95" s="12">
         <v>20.9</v>
       </c>
-      <c r="E95" s="4">
+      <c r="E95" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="F95" s="4">
         <v>67</v>
-      </c>
-      <c r="F95" s="4">
-        <v>14</v>
       </c>
       <c r="G95" s="4">
         <v>14</v>
       </c>
       <c r="H95" s="4">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I95" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J95" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A96" s="10">
         <v>43282</v>
       </c>
@@ -2696,23 +3335,26 @@
       <c r="D96" s="12">
         <v>22.3</v>
       </c>
-      <c r="E96" s="4">
+      <c r="E96" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="F96" s="4">
         <v>69</v>
-      </c>
-      <c r="F96" s="4">
-        <v>13</v>
       </c>
       <c r="G96" s="4">
         <v>13</v>
       </c>
       <c r="H96" s="4">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I96" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J96" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A97" s="10">
         <v>43313</v>
       </c>
@@ -2725,23 +3367,26 @@
       <c r="D97" s="12">
         <v>22.8</v>
       </c>
-      <c r="E97" s="4">
+      <c r="E97" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F97" s="4">
         <v>70</v>
-      </c>
-      <c r="F97" s="4">
-        <v>9</v>
       </c>
       <c r="G97" s="4">
         <v>9</v>
       </c>
       <c r="H97" s="4">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I97" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J97" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A98" s="10">
         <v>43344</v>
       </c>
@@ -2754,23 +3399,26 @@
       <c r="D98" s="12">
         <v>17.600000000000001</v>
       </c>
-      <c r="E98" s="4">
+      <c r="E98" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="F98" s="4">
         <v>76</v>
-      </c>
-      <c r="F98" s="4">
-        <v>9</v>
       </c>
       <c r="G98" s="4">
         <v>9</v>
       </c>
       <c r="H98" s="4">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I98" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J98" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A99" s="10">
         <v>43374</v>
       </c>
@@ -2783,23 +3431,26 @@
       <c r="D99" s="12">
         <v>13.2</v>
       </c>
-      <c r="E99" s="4">
+      <c r="E99" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="F99" s="4">
         <v>82</v>
-      </c>
-      <c r="F99" s="4">
-        <v>12</v>
       </c>
       <c r="G99" s="4">
         <v>12</v>
       </c>
       <c r="H99" s="4">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I99" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J99" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A100" s="10">
         <v>43405</v>
       </c>
@@ -2812,23 +3463,26 @@
       <c r="D100" s="12">
         <v>8.3000000000000007</v>
       </c>
-      <c r="E100" s="4">
+      <c r="E100" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="F100" s="4">
         <v>84</v>
-      </c>
-      <c r="F100" s="4">
-        <v>17</v>
       </c>
       <c r="G100" s="4">
         <v>17</v>
       </c>
       <c r="H100" s="4">
+        <v>17</v>
+      </c>
+      <c r="I100" s="4">
         <v>2</v>
       </c>
-      <c r="I100" s="4">
+      <c r="J100" s="4">
         <v>3</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A101" s="10">
         <v>43435</v>
       </c>
@@ -2841,23 +3495,26 @@
       <c r="D101" s="12">
         <v>2.2000000000000002</v>
       </c>
-      <c r="E101" s="4">
+      <c r="E101" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="F101" s="4">
         <v>84</v>
       </c>
-      <c r="F101" s="4">
+      <c r="G101" s="4">
         <v>9</v>
       </c>
-      <c r="G101" s="4">
+      <c r="H101" s="4">
         <v>8</v>
-      </c>
-      <c r="H101" s="4">
-        <v>1</v>
       </c>
       <c r="I101" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J101" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A102" s="10">
         <v>43466</v>
       </c>
@@ -2870,23 +3527,26 @@
       <c r="D102" s="12">
         <v>0.7</v>
       </c>
-      <c r="E102" s="4">
+      <c r="E102" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="F102" s="4">
         <v>76</v>
       </c>
-      <c r="F102" s="4">
+      <c r="G102" s="4">
         <v>8</v>
-      </c>
-      <c r="G102" s="4">
-        <v>6</v>
       </c>
       <c r="H102" s="4">
         <v>6</v>
       </c>
       <c r="I102" s="4">
+        <v>6</v>
+      </c>
+      <c r="J102" s="4">
         <v>5</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A103" s="10">
         <v>43497</v>
       </c>
@@ -2899,23 +3559,26 @@
       <c r="D103" s="12">
         <v>4.9000000000000004</v>
       </c>
-      <c r="E103" s="4">
+      <c r="E103" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="F103" s="4">
         <v>69</v>
-      </c>
-      <c r="F103" s="4">
-        <v>6</v>
       </c>
       <c r="G103" s="4">
         <v>6</v>
       </c>
       <c r="H103" s="4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I103" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J103" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A104" s="10">
         <v>43525</v>
       </c>
@@ -2928,23 +3591,26 @@
       <c r="D104" s="12">
         <v>9</v>
       </c>
-      <c r="E104" s="4">
+      <c r="E104" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="F104" s="4">
         <v>64</v>
-      </c>
-      <c r="F104" s="4">
-        <v>9</v>
       </c>
       <c r="G104" s="4">
         <v>9</v>
       </c>
       <c r="H104" s="4">
+        <v>9</v>
+      </c>
+      <c r="I104" s="4">
         <v>2</v>
       </c>
-      <c r="I104" s="4">
+      <c r="J104" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A105" s="10">
         <v>43556</v>
       </c>
@@ -2957,23 +3623,26 @@
       <c r="D105" s="12">
         <v>11.6</v>
       </c>
-      <c r="E105" s="4">
+      <c r="E105" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="F105" s="4">
         <v>73</v>
-      </c>
-      <c r="F105" s="4">
-        <v>17</v>
       </c>
       <c r="G105" s="4">
         <v>17</v>
       </c>
       <c r="H105" s="4">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="I105" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J105" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A106" s="10">
         <v>43586</v>
       </c>
@@ -2986,23 +3655,26 @@
       <c r="D106" s="12">
         <v>12.9</v>
       </c>
-      <c r="E106" s="4">
+      <c r="E106" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="F106" s="4">
         <v>77</v>
-      </c>
-      <c r="F106" s="4">
-        <v>23</v>
       </c>
       <c r="G106" s="4">
         <v>23</v>
       </c>
       <c r="H106" s="4">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="I106" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J106" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A107" s="10">
         <v>43617</v>
       </c>
@@ -3015,23 +3687,26 @@
       <c r="D107" s="12">
         <v>23.5</v>
       </c>
-      <c r="E107" s="4">
+      <c r="E107" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="F107" s="4">
         <v>66</v>
-      </c>
-      <c r="F107" s="4">
-        <v>9</v>
       </c>
       <c r="G107" s="4">
         <v>9</v>
       </c>
       <c r="H107" s="4">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I107" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J107" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A108" s="10">
         <v>43647</v>
       </c>
@@ -3044,23 +3719,26 @@
       <c r="D108" s="12">
         <v>22.9</v>
       </c>
-      <c r="E108" s="4">
+      <c r="E108" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="F108" s="4">
         <v>68</v>
-      </c>
-      <c r="F108" s="4">
-        <v>15</v>
       </c>
       <c r="G108" s="4">
         <v>15</v>
       </c>
       <c r="H108" s="4">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I108" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J108" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A109" s="10">
         <v>43678</v>
       </c>
@@ -3073,23 +3751,26 @@
       <c r="D109" s="12">
         <v>22.6</v>
       </c>
-      <c r="E109" s="4">
+      <c r="E109" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="F109" s="4">
         <v>74</v>
-      </c>
-      <c r="F109" s="4">
-        <v>14</v>
       </c>
       <c r="G109" s="4">
         <v>14</v>
       </c>
       <c r="H109" s="4">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I109" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J109" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A110" s="10">
         <v>43709</v>
       </c>
@@ -3102,23 +3783,26 @@
       <c r="D110" s="12">
         <v>16.8</v>
       </c>
-      <c r="E110" s="4">
+      <c r="E110" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="F110" s="4">
         <v>78</v>
-      </c>
-      <c r="F110" s="4">
-        <v>11</v>
       </c>
       <c r="G110" s="4">
         <v>11</v>
       </c>
       <c r="H110" s="4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I110" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J110" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A111" s="10">
         <v>43739</v>
       </c>
@@ -3131,23 +3815,26 @@
       <c r="D111" s="12">
         <v>13.2</v>
       </c>
-      <c r="E111" s="4">
+      <c r="E111" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="F111" s="4">
         <v>75</v>
-      </c>
-      <c r="F111" s="4">
-        <v>9</v>
       </c>
       <c r="G111" s="4">
         <v>9</v>
       </c>
       <c r="H111" s="4">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I111" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J111" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A112" s="10">
         <v>43770</v>
       </c>
@@ -3160,23 +3847,26 @@
       <c r="D112" s="12">
         <v>8.8000000000000007</v>
       </c>
-      <c r="E112" s="4">
+      <c r="E112" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="F112" s="4">
         <v>85</v>
-      </c>
-      <c r="F112" s="4">
-        <v>28</v>
       </c>
       <c r="G112" s="4">
         <v>28</v>
       </c>
       <c r="H112" s="4">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="I112" s="4">
+        <v>0</v>
+      </c>
+      <c r="J112" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A113" s="10">
         <v>43800</v>
       </c>
@@ -3189,23 +3879,26 @@
       <c r="D113" s="12">
         <v>3.6</v>
       </c>
-      <c r="E113" s="4">
+      <c r="E113" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="F113" s="4">
         <v>81</v>
-      </c>
-      <c r="F113" s="4">
-        <v>13</v>
       </c>
       <c r="G113" s="4">
         <v>13</v>
       </c>
       <c r="H113" s="4">
+        <v>13</v>
+      </c>
+      <c r="I113" s="4">
         <v>2</v>
       </c>
-      <c r="I113" s="4">
+      <c r="J113" s="4">
         <v>3</v>
       </c>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A114" s="10">
         <v>43831</v>
       </c>
@@ -3218,23 +3911,26 @@
       <c r="D114" s="12">
         <v>1.9</v>
       </c>
-      <c r="E114" s="4">
+      <c r="E114" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="F114" s="4">
         <v>77</v>
-      </c>
-      <c r="F114" s="4">
-        <v>5</v>
       </c>
       <c r="G114" s="4">
         <v>5</v>
       </c>
       <c r="H114" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I114" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J114" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A115" s="10">
         <v>43862</v>
       </c>
@@ -3247,23 +3943,26 @@
       <c r="D115" s="12">
         <v>6.8</v>
       </c>
-      <c r="E115" s="4">
+      <c r="E115" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="F115" s="4">
         <v>63</v>
-      </c>
-      <c r="F115" s="4">
-        <v>7</v>
       </c>
       <c r="G115" s="4">
         <v>7</v>
       </c>
       <c r="H115" s="4">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I115" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J115" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A116" s="10">
         <v>43891</v>
       </c>
@@ -3276,23 +3975,26 @@
       <c r="D116" s="12">
         <v>7.2</v>
       </c>
-      <c r="E116" s="4">
+      <c r="E116" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="F116" s="4">
         <v>62</v>
       </c>
-      <c r="F116" s="4">
+      <c r="G116" s="4">
         <v>14</v>
       </c>
-      <c r="G116" s="4">
+      <c r="H116" s="4">
         <v>12</v>
       </c>
-      <c r="H116" s="4">
-        <v>0</v>
-      </c>
       <c r="I116" s="4">
+        <v>0</v>
+      </c>
+      <c r="J116" s="4">
         <v>4</v>
       </c>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A117" s="10">
         <v>43922</v>
       </c>
@@ -3305,23 +4007,26 @@
       <c r="D117" s="12">
         <v>13</v>
       </c>
-      <c r="E117" s="4">
+      <c r="E117" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="F117" s="4">
         <v>50</v>
-      </c>
-      <c r="F117" s="4">
-        <v>3</v>
       </c>
       <c r="G117" s="4">
         <v>3</v>
       </c>
       <c r="H117" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I117" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J117" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A118" s="10">
         <v>43952</v>
       </c>
@@ -3334,23 +4039,26 @@
       <c r="D118" s="12">
         <v>15.3</v>
       </c>
-      <c r="E118" s="4">
+      <c r="E118" s="20" t="s">
+        <v>103</v>
+      </c>
+      <c r="F118" s="4">
         <v>66</v>
-      </c>
-      <c r="F118" s="4">
-        <v>13</v>
       </c>
       <c r="G118" s="4">
         <v>13</v>
       </c>
       <c r="H118" s="4">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I118" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J118" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A119" s="10">
         <v>43983</v>
       </c>
@@ -3363,23 +4071,26 @@
       <c r="D119" s="12">
         <v>19.600000000000001</v>
       </c>
-      <c r="E119" s="4">
+      <c r="E119" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="F119" s="4">
         <v>69</v>
-      </c>
-      <c r="F119" s="4">
-        <v>17</v>
       </c>
       <c r="G119" s="4">
         <v>17</v>
       </c>
       <c r="H119" s="4">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="I119" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J119" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A120" s="10">
         <v>44013</v>
       </c>
@@ -3392,23 +4103,26 @@
       <c r="D120" s="12">
         <v>21.8</v>
       </c>
-      <c r="E120" s="4">
+      <c r="E120" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="F120" s="4">
         <v>65</v>
-      </c>
-      <c r="F120" s="4">
-        <v>11</v>
       </c>
       <c r="G120" s="4">
         <v>11</v>
       </c>
       <c r="H120" s="4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I120" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J120" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A121" s="10">
         <v>44044</v>
       </c>
@@ -3421,23 +4135,26 @@
       <c r="D121" s="12">
         <v>22.2</v>
       </c>
-      <c r="E121" s="4">
+      <c r="E121" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F121" s="4">
         <v>68</v>
-      </c>
-      <c r="F121" s="4">
-        <v>11</v>
       </c>
       <c r="G121" s="4">
         <v>11</v>
       </c>
       <c r="H121" s="4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I121" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J121" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A122" s="10">
         <v>44075</v>
       </c>
@@ -3450,23 +4167,26 @@
       <c r="D122" s="12">
         <v>17.5</v>
       </c>
-      <c r="E122" s="4">
+      <c r="E122" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="F122" s="4">
         <v>76</v>
-      </c>
-      <c r="F122" s="4">
-        <v>10</v>
       </c>
       <c r="G122" s="4">
         <v>10</v>
       </c>
       <c r="H122" s="4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I122" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J122" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A123" s="10">
         <v>44105</v>
       </c>
@@ -3479,23 +4199,26 @@
       <c r="D123" s="12">
         <v>11.9</v>
       </c>
-      <c r="E123" s="4">
+      <c r="E123" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="F123" s="4">
         <v>82</v>
-      </c>
-      <c r="F123" s="4">
-        <v>18</v>
       </c>
       <c r="G123" s="4">
         <v>18</v>
       </c>
       <c r="H123" s="4">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I123" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J123" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A124" s="10">
         <v>44136</v>
       </c>
@@ -3508,23 +4231,26 @@
       <c r="D124" s="12">
         <v>5.3</v>
       </c>
-      <c r="E124" s="4">
+      <c r="E124" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="F124" s="4">
         <v>85</v>
-      </c>
-      <c r="F124" s="4">
-        <v>11</v>
       </c>
       <c r="G124" s="4">
         <v>11</v>
       </c>
       <c r="H124" s="4">
+        <v>11</v>
+      </c>
+      <c r="I124" s="4">
         <v>2</v>
       </c>
-      <c r="I124" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J124" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A125" s="10">
         <v>44166</v>
       </c>
@@ -3537,23 +4263,26 @@
       <c r="D125" s="12">
         <v>2.9</v>
       </c>
-      <c r="E125" s="4">
+      <c r="E125" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="F125" s="4">
         <v>87</v>
       </c>
-      <c r="F125" s="4">
+      <c r="G125" s="4">
         <v>20</v>
       </c>
-      <c r="G125" s="4">
+      <c r="H125" s="4">
         <v>17</v>
       </c>
-      <c r="H125" s="4">
+      <c r="I125" s="4">
         <v>1</v>
       </c>
-      <c r="I125" s="4">
+      <c r="J125" s="4">
         <v>5</v>
       </c>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A126" s="10">
         <v>44197</v>
       </c>
@@ -3566,26 +4295,29 @@
       <c r="D126" s="12">
         <v>1.2</v>
       </c>
-      <c r="E126" s="4">
+      <c r="E126" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="F126" s="4">
         <v>87</v>
       </c>
-      <c r="F126" s="4">
+      <c r="G126" s="4">
         <v>18</v>
       </c>
-      <c r="G126" s="4">
+      <c r="H126" s="4">
         <v>16</v>
       </c>
-      <c r="H126" s="4">
+      <c r="I126" s="4">
         <v>5</v>
       </c>
-      <c r="I126" s="4">
+      <c r="J126" s="4">
         <v>7</v>
       </c>
-      <c r="J126" s="4">
+      <c r="K126" s="4">
         <v>8</v>
       </c>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A127" s="10">
         <v>44228</v>
       </c>
@@ -3598,26 +4330,29 @@
       <c r="D127" s="12">
         <v>5.9</v>
       </c>
-      <c r="E127" s="4">
+      <c r="E127" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="F127" s="4">
         <v>74</v>
       </c>
-      <c r="F127" s="4">
+      <c r="G127" s="4">
         <v>10</v>
       </c>
-      <c r="G127" s="4">
+      <c r="H127" s="4">
         <v>9</v>
       </c>
-      <c r="H127" s="4">
+      <c r="I127" s="4">
         <v>2</v>
       </c>
-      <c r="I127" s="4">
+      <c r="J127" s="4">
         <v>3</v>
       </c>
-      <c r="J127" s="4">
+      <c r="K127" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A128" s="10">
         <v>44256</v>
       </c>
@@ -3630,26 +4365,29 @@
       <c r="D128" s="12">
         <v>6.7</v>
       </c>
-      <c r="E128" s="4">
+      <c r="E128" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="F128" s="4">
         <v>63</v>
-      </c>
-      <c r="F128" s="4">
-        <v>6</v>
       </c>
       <c r="G128" s="4">
         <v>6</v>
       </c>
       <c r="H128" s="4">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I128" s="4">
         <v>1</v>
       </c>
       <c r="J128" s="4">
+        <v>1</v>
+      </c>
+      <c r="K128" s="4">
         <v>2</v>
       </c>
     </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A129" s="10">
         <v>44287</v>
       </c>
@@ -3662,26 +4400,29 @@
       <c r="D129" s="12">
         <v>9.1</v>
       </c>
-      <c r="E129" s="4">
+      <c r="E129" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="F129" s="4">
         <v>65</v>
-      </c>
-      <c r="F129" s="4">
-        <v>15</v>
       </c>
       <c r="G129" s="4">
         <v>15</v>
       </c>
       <c r="H129" s="4">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="I129" s="4">
         <v>4</v>
       </c>
       <c r="J129" s="4">
+        <v>4</v>
+      </c>
+      <c r="K129" s="4">
         <v>3</v>
       </c>
     </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A130" s="10">
         <v>44317</v>
       </c>
@@ -3694,17 +4435,17 @@
       <c r="D130" s="12">
         <v>13.5</v>
       </c>
-      <c r="E130" s="4">
+      <c r="E130" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="F130" s="4">
         <v>70</v>
-      </c>
-      <c r="F130" s="4">
-        <v>23</v>
       </c>
       <c r="G130" s="4">
         <v>23</v>
       </c>
       <c r="H130" s="4">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="I130" s="4">
         <v>0</v>
@@ -3712,8 +4453,11 @@
       <c r="J130" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K130" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A131" s="10">
         <v>44348</v>
       </c>
@@ -3726,17 +4470,17 @@
       <c r="D131" s="12">
         <v>23.1</v>
       </c>
-      <c r="E131" s="4">
+      <c r="E131" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="F131" s="4">
         <v>58</v>
-      </c>
-      <c r="F131" s="4">
-        <v>5</v>
       </c>
       <c r="G131" s="4">
         <v>5</v>
       </c>
       <c r="H131" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I131" s="4">
         <v>0</v>
@@ -3744,8 +4488,11 @@
       <c r="J131" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K131" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A132" s="10">
         <v>44378</v>
       </c>
@@ -3758,17 +4505,17 @@
       <c r="D132" s="12">
         <v>23.3</v>
       </c>
-      <c r="E132" s="4">
+      <c r="E132" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="F132" s="4">
         <v>64</v>
-      </c>
-      <c r="F132" s="4">
-        <v>12</v>
       </c>
       <c r="G132" s="4">
         <v>12</v>
       </c>
       <c r="H132" s="4">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I132" s="4">
         <v>0</v>
@@ -3776,8 +4523,11 @@
       <c r="J132" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K132" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A133" s="10">
         <v>44409</v>
       </c>
@@ -3790,17 +4540,17 @@
       <c r="D133" s="12">
         <v>21.1</v>
       </c>
-      <c r="E133" s="4">
+      <c r="E133" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="F133" s="4">
         <v>67</v>
-      </c>
-      <c r="F133" s="4">
-        <v>15</v>
       </c>
       <c r="G133" s="4">
         <v>15</v>
       </c>
       <c r="H133" s="4">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I133" s="4">
         <v>0</v>
@@ -3808,8 +4558,11 @@
       <c r="J133" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K133" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A134" s="10">
         <v>44440</v>
       </c>
@@ -3822,17 +4575,17 @@
       <c r="D134" s="12">
         <v>17.5</v>
       </c>
-      <c r="E134" s="4">
+      <c r="E134" s="20" t="s">
+        <v>113</v>
+      </c>
+      <c r="F134" s="4">
         <v>68</v>
-      </c>
-      <c r="F134" s="4">
-        <v>7</v>
       </c>
       <c r="G134" s="4">
         <v>7</v>
       </c>
       <c r="H134" s="4">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I134" s="4">
         <v>0</v>
@@ -3840,8 +4593,11 @@
       <c r="J134" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K134" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A135" s="10">
         <v>44470</v>
       </c>
@@ -3854,17 +4610,17 @@
       <c r="D135" s="12">
         <v>9.8000000000000007</v>
       </c>
-      <c r="E135" s="4">
+      <c r="E135" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="F135" s="4">
         <v>78</v>
-      </c>
-      <c r="F135" s="4">
-        <v>11</v>
       </c>
       <c r="G135" s="4">
         <v>11</v>
       </c>
       <c r="H135" s="4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I135" s="4">
         <v>0</v>
@@ -3872,8 +4628,11 @@
       <c r="J135" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K135" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A136" s="10">
         <v>44501</v>
       </c>
@@ -3886,26 +4645,29 @@
       <c r="D136" s="12">
         <v>5.9</v>
       </c>
-      <c r="E136" s="4">
+      <c r="E136" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="F136" s="4">
         <v>83</v>
       </c>
-      <c r="F136" s="4">
+      <c r="G136" s="4">
         <v>15</v>
       </c>
-      <c r="G136" s="4">
+      <c r="H136" s="4">
         <v>14</v>
       </c>
-      <c r="H136" s="4">
-        <v>0</v>
-      </c>
       <c r="I136" s="4">
+        <v>0</v>
+      </c>
+      <c r="J136" s="4">
         <v>2</v>
       </c>
-      <c r="J136" s="4">
+      <c r="K136" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A137" s="10">
         <v>44531</v>
       </c>
@@ -3918,26 +4680,29 @@
       <c r="D137" s="12">
         <v>1.3</v>
       </c>
-      <c r="E137" s="4">
+      <c r="E137" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="F137" s="4">
         <v>88</v>
       </c>
-      <c r="F137" s="4">
+      <c r="G137" s="4">
         <v>12</v>
       </c>
-      <c r="G137" s="4">
+      <c r="H137" s="4">
         <v>10</v>
       </c>
-      <c r="H137" s="4">
+      <c r="I137" s="4">
         <v>4</v>
       </c>
-      <c r="I137" s="4">
+      <c r="J137" s="4">
         <v>5</v>
       </c>
-      <c r="J137" s="4">
+      <c r="K137" s="4">
         <v>12</v>
       </c>
     </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A138" s="10">
         <v>44562</v>
       </c>
@@ -3950,26 +4715,29 @@
       <c r="D138" s="14">
         <v>0.8</v>
       </c>
-      <c r="E138" s="4">
+      <c r="E138" s="21" t="s">
+        <v>97</v>
+      </c>
+      <c r="F138" s="4">
         <v>81</v>
-      </c>
-      <c r="F138" s="4">
-        <v>4</v>
       </c>
       <c r="G138" s="4">
         <v>4</v>
       </c>
       <c r="H138" s="4">
+        <v>4</v>
+      </c>
+      <c r="I138" s="4">
         <v>1</v>
       </c>
-      <c r="I138" s="4">
+      <c r="J138" s="4">
         <v>2</v>
       </c>
-      <c r="J138" s="4">
+      <c r="K138" s="4">
         <v>17</v>
       </c>
     </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A139" s="10">
         <v>44593</v>
       </c>
@@ -3982,26 +4750,29 @@
       <c r="D139" s="12">
         <v>5.0999999999999996</v>
       </c>
-      <c r="E139" s="4">
+      <c r="E139" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="F139" s="4">
         <v>70</v>
-      </c>
-      <c r="F139" s="4">
-        <v>10</v>
       </c>
       <c r="G139" s="4">
         <v>10</v>
       </c>
       <c r="H139" s="4">
+        <v>10</v>
+      </c>
+      <c r="I139" s="4">
         <v>2</v>
       </c>
-      <c r="I139" s="4">
+      <c r="J139" s="4">
         <v>1</v>
       </c>
-      <c r="J139" s="4">
+      <c r="K139" s="4">
         <v>2</v>
       </c>
     </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A140" s="10">
         <v>44621</v>
       </c>
@@ -4014,17 +4785,17 @@
       <c r="D140" s="12">
         <v>6.6</v>
       </c>
-      <c r="E140" s="4">
+      <c r="E140" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="F140" s="4">
         <v>52</v>
-      </c>
-      <c r="F140" s="4">
-        <v>1</v>
       </c>
       <c r="G140" s="4">
         <v>1</v>
       </c>
       <c r="H140" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I140" s="4">
         <v>0</v>
@@ -4032,8 +4803,11 @@
       <c r="J140" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K140" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A141" s="10">
         <v>44652</v>
       </c>
@@ -4046,26 +4820,29 @@
       <c r="D141" s="12">
         <v>10.4</v>
       </c>
-      <c r="E141" s="4">
+      <c r="E141" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="F141" s="4">
         <v>64</v>
-      </c>
-      <c r="F141" s="4">
-        <v>14</v>
       </c>
       <c r="G141" s="4">
         <v>14</v>
       </c>
       <c r="H141" s="4">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="I141" s="4">
         <v>3</v>
       </c>
       <c r="J141" s="4">
+        <v>3</v>
+      </c>
+      <c r="K141" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A142" s="10">
         <v>44682</v>
       </c>
@@ -4078,17 +4855,17 @@
       <c r="D142" s="12">
         <v>18.100000000000001</v>
       </c>
-      <c r="E142" s="4">
+      <c r="E142" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="F142" s="4">
         <v>64</v>
-      </c>
-      <c r="F142" s="4">
-        <v>13</v>
       </c>
       <c r="G142" s="4">
         <v>13</v>
       </c>
       <c r="H142" s="4">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I142" s="4">
         <v>0</v>
@@ -4096,8 +4873,11 @@
       <c r="J142" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K142" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A143" s="10">
         <v>44713</v>
       </c>
@@ -4110,17 +4890,17 @@
       <c r="D143" s="12">
         <v>23.4</v>
       </c>
-      <c r="E143" s="4">
+      <c r="E143" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="F143" s="4">
         <v>60</v>
-      </c>
-      <c r="F143" s="4">
-        <v>11</v>
       </c>
       <c r="G143" s="4">
         <v>11</v>
       </c>
       <c r="H143" s="4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I143" s="4">
         <v>0</v>
@@ -4128,8 +4908,11 @@
       <c r="J143" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K143" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A144" s="10">
         <v>44743</v>
       </c>
@@ -4142,17 +4925,17 @@
       <c r="D144" s="12">
         <v>24.5</v>
       </c>
-      <c r="E144" s="4">
+      <c r="E144" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="F144" s="4">
         <v>57</v>
-      </c>
-      <c r="F144" s="4">
-        <v>13</v>
       </c>
       <c r="G144" s="4">
         <v>13</v>
       </c>
       <c r="H144" s="4">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I144" s="4">
         <v>0</v>
@@ -4160,8 +4943,11 @@
       <c r="J144" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K144" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A145" s="10">
         <v>44774</v>
       </c>
@@ -4174,17 +4960,17 @@
       <c r="D145" s="12">
         <v>23</v>
       </c>
-      <c r="E145" s="4">
+      <c r="E145" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="F145" s="4">
         <v>62</v>
-      </c>
-      <c r="F145" s="4">
-        <v>12</v>
       </c>
       <c r="G145" s="4">
         <v>12</v>
       </c>
       <c r="H145" s="4">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I145" s="4">
         <v>0</v>
@@ -4192,8 +4978,11 @@
       <c r="J145" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K145" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A146" s="10">
         <v>44805</v>
       </c>
@@ -4206,17 +4995,17 @@
       <c r="D146" s="12">
         <v>16</v>
       </c>
-      <c r="E146" s="4">
+      <c r="E146" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="F146" s="4">
         <v>76</v>
-      </c>
-      <c r="F146" s="4">
-        <v>16</v>
       </c>
       <c r="G146" s="4">
         <v>16</v>
       </c>
       <c r="H146" s="4">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I146" s="4">
         <v>0</v>
@@ -4224,8 +5013,11 @@
       <c r="J146" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K146" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A147" s="10">
         <v>44835</v>
       </c>
@@ -4238,26 +5030,29 @@
       <c r="D147" s="12">
         <v>14.4</v>
       </c>
-      <c r="E147" s="4">
+      <c r="E147" s="20" t="s">
+        <v>122</v>
+      </c>
+      <c r="F147" s="4">
         <v>78</v>
       </c>
-      <c r="F147" s="4">
+      <c r="G147" s="4">
         <v>9</v>
       </c>
-      <c r="G147" s="4">
+      <c r="H147" s="4">
         <v>8</v>
       </c>
-      <c r="H147" s="4">
-        <v>0</v>
-      </c>
       <c r="I147" s="4">
         <v>0</v>
       </c>
       <c r="J147" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K147" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A148" s="10">
         <v>44866</v>
       </c>
@@ -4270,17 +5065,17 @@
       <c r="D148" s="12">
         <v>7.9</v>
       </c>
-      <c r="E148" s="4">
+      <c r="E148" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="F148" s="4">
         <v>80</v>
-      </c>
-      <c r="F148" s="4">
-        <v>15</v>
       </c>
       <c r="G148" s="4">
         <v>15</v>
       </c>
       <c r="H148" s="4">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I148" s="4">
         <v>0</v>
@@ -4288,8 +5083,11 @@
       <c r="J148" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K148" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A149" s="10">
         <v>44896</v>
       </c>
@@ -4302,26 +5100,29 @@
       <c r="D149" s="12">
         <v>4.4000000000000004</v>
       </c>
-      <c r="E149" s="4">
+      <c r="E149" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="F149" s="4">
         <v>81</v>
-      </c>
-      <c r="F149" s="4">
-        <v>18</v>
       </c>
       <c r="G149" s="4">
         <v>18</v>
       </c>
       <c r="H149" s="4">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="I149" s="4">
         <v>5</v>
       </c>
       <c r="J149" s="4">
+        <v>5</v>
+      </c>
+      <c r="K149" s="4">
         <v>2</v>
       </c>
     </row>
-    <row r="150" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A150" s="10">
         <v>44927</v>
       </c>
@@ -4334,26 +5135,29 @@
       <c r="D150" s="12">
         <v>3.8</v>
       </c>
-      <c r="E150" s="4">
+      <c r="E150" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="F150" s="4">
         <v>79</v>
       </c>
-      <c r="F150" s="4">
+      <c r="G150" s="4">
         <v>13</v>
       </c>
-      <c r="G150" s="4">
+      <c r="H150" s="4">
         <v>12</v>
       </c>
-      <c r="H150" s="4">
+      <c r="I150" s="4">
         <v>7</v>
       </c>
-      <c r="I150" s="4">
+      <c r="J150" s="4">
         <v>8</v>
       </c>
-      <c r="J150" s="4">
+      <c r="K150" s="4">
         <v>16</v>
       </c>
     </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A151" s="10">
         <v>44958</v>
       </c>
@@ -4366,26 +5170,29 @@
       <c r="D151" s="12">
         <v>3.6</v>
       </c>
-      <c r="E151" s="4">
+      <c r="E151" s="20" t="s">
+        <v>125</v>
+      </c>
+      <c r="F151" s="4">
         <v>72</v>
       </c>
-      <c r="F151" s="4">
+      <c r="G151" s="4">
         <v>4</v>
       </c>
-      <c r="G151" s="4">
+      <c r="H151" s="4">
         <v>2</v>
       </c>
-      <c r="H151" s="4">
-        <v>0</v>
-      </c>
       <c r="I151" s="4">
+        <v>0</v>
+      </c>
+      <c r="J151" s="4">
         <v>3</v>
       </c>
-      <c r="J151" s="4">
+      <c r="K151" s="4">
         <v>7</v>
       </c>
     </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A152" s="10">
         <v>44986</v>
       </c>
@@ -4398,26 +5205,29 @@
       <c r="D152" s="12">
         <v>8.6</v>
       </c>
-      <c r="E152" s="4">
+      <c r="E152" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="F152" s="4">
         <v>68</v>
-      </c>
-      <c r="F152" s="4">
-        <v>11</v>
       </c>
       <c r="G152" s="4">
         <v>11</v>
       </c>
       <c r="H152" s="4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I152" s="4">
+        <v>0</v>
+      </c>
+      <c r="J152" s="4">
         <v>1</v>
       </c>
-      <c r="J152" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K152" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A153" s="10">
         <v>45017</v>
       </c>
@@ -4430,17 +5240,17 @@
       <c r="D153" s="12">
         <v>10.199999999999999</v>
       </c>
-      <c r="E153" s="4">
+      <c r="E153" s="20" t="s">
+        <v>126</v>
+      </c>
+      <c r="F153" s="4">
         <v>66</v>
-      </c>
-      <c r="F153" s="4">
-        <v>13</v>
       </c>
       <c r="G153" s="4">
         <v>13</v>
       </c>
       <c r="H153" s="4">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I153" s="4">
         <v>0</v>
@@ -4448,8 +5258,11 @@
       <c r="J153" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K153" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A154" s="10">
         <v>45047</v>
       </c>
@@ -4462,17 +5275,17 @@
       <c r="D154" s="12">
         <v>15.9</v>
       </c>
-      <c r="E154" s="4">
+      <c r="E154" s="20" t="s">
+        <v>103</v>
+      </c>
+      <c r="F154" s="4">
         <v>71</v>
-      </c>
-      <c r="F154" s="4">
-        <v>17</v>
       </c>
       <c r="G154" s="4">
         <v>17</v>
       </c>
       <c r="H154" s="4">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="I154" s="4">
         <v>0</v>
@@ -4480,8 +5293,11 @@
       <c r="J154" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K154" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A155" s="10">
         <v>45078</v>
       </c>
@@ -4494,17 +5310,17 @@
       <c r="D155" s="12">
         <v>21</v>
       </c>
-      <c r="E155" s="4">
+      <c r="E155" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="F155" s="4">
         <v>66</v>
-      </c>
-      <c r="F155" s="4">
-        <v>13</v>
       </c>
       <c r="G155" s="4">
         <v>13</v>
       </c>
       <c r="H155" s="4">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I155" s="4">
         <v>0</v>
@@ -4512,8 +5328,11 @@
       <c r="J155" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="156" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K155" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A156" s="10">
         <v>45108</v>
       </c>
@@ -4526,17 +5345,17 @@
       <c r="D156" s="12">
         <v>22.7</v>
       </c>
-      <c r="E156" s="4">
+      <c r="E156" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F156" s="4">
         <v>68</v>
-      </c>
-      <c r="F156" s="4">
-        <v>14</v>
       </c>
       <c r="G156" s="4">
         <v>14</v>
       </c>
       <c r="H156" s="4">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I156" s="4">
         <v>0</v>
@@ -4544,8 +5363,11 @@
       <c r="J156" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K156" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A157" s="10">
         <v>45139</v>
       </c>
@@ -4558,20 +5380,23 @@
       <c r="D157" s="12">
         <v>21.8</v>
       </c>
-      <c r="E157" s="4">
+      <c r="E157" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="F157" s="4">
         <v>70</v>
       </c>
-      <c r="H157" s="4">
-        <v>0</v>
-      </c>
       <c r="I157" s="4">
         <v>0</v>
       </c>
       <c r="J157" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K157" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A158" s="10">
         <v>45170</v>
       </c>
@@ -4584,20 +5409,23 @@
       <c r="D158" s="12">
         <v>19.100000000000001</v>
       </c>
-      <c r="E158" s="4">
+      <c r="E158" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="F158" s="4">
         <v>76</v>
       </c>
-      <c r="H158" s="4">
-        <v>0</v>
-      </c>
       <c r="I158" s="4">
         <v>0</v>
       </c>
       <c r="J158" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="159" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K158" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A159" s="10">
         <v>45200</v>
       </c>
@@ -4610,20 +5438,23 @@
       <c r="D159" s="12">
         <v>15</v>
       </c>
-      <c r="E159" s="4">
+      <c r="E159" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="F159" s="4">
         <v>82</v>
       </c>
-      <c r="H159" s="4">
-        <v>0</v>
-      </c>
       <c r="I159" s="4">
         <v>0</v>
       </c>
       <c r="J159" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="160" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K159" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A160" s="10">
         <v>45231</v>
       </c>
@@ -4636,11 +5467,11 @@
       <c r="D160" s="12">
         <v>6.9</v>
       </c>
-      <c r="E160" s="4">
+      <c r="E160" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="F160" s="4">
         <v>82</v>
-      </c>
-      <c r="H160" s="4">
-        <v>1</v>
       </c>
       <c r="I160" s="4">
         <v>1</v>
@@ -4648,8 +5479,11 @@
       <c r="J160" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="161" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K160" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A161" s="10">
         <v>45261</v>
       </c>
@@ -4662,20 +5496,23 @@
       <c r="D161" s="12">
         <v>4.3</v>
       </c>
-      <c r="E161" s="4">
+      <c r="E161" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="F161" s="4">
         <v>83</v>
       </c>
-      <c r="H161" s="4">
+      <c r="I161" s="4">
         <v>2</v>
       </c>
-      <c r="I161" s="4">
+      <c r="J161" s="4">
         <v>4</v>
       </c>
-      <c r="J161" s="4">
+      <c r="K161" s="4">
         <v>5</v>
       </c>
     </row>
-    <row r="162" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A162" s="10">
         <v>45292</v>
       </c>
@@ -4688,20 +5525,23 @@
       <c r="D162" s="12">
         <v>1.6</v>
       </c>
-      <c r="E162" s="4">
+      <c r="E162" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="F162" s="4">
         <v>77</v>
       </c>
-      <c r="H162" s="4">
+      <c r="I162" s="4">
         <v>1</v>
       </c>
-      <c r="I162" s="4">
+      <c r="J162" s="4">
         <v>2</v>
       </c>
-      <c r="J162" s="4">
+      <c r="K162" s="4">
         <v>12</v>
       </c>
     </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A163" s="10">
         <v>45323</v>
       </c>
@@ -4714,20 +5554,23 @@
       <c r="D163" s="12">
         <v>7.6</v>
       </c>
-      <c r="E163" s="4">
+      <c r="E163" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F163" s="4">
         <v>75</v>
       </c>
-      <c r="H163" s="4">
-        <v>0</v>
-      </c>
       <c r="I163" s="4">
         <v>0</v>
       </c>
       <c r="J163" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K163" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A164" s="10">
         <v>45352</v>
       </c>
@@ -4740,20 +5583,23 @@
       <c r="D164" s="12">
         <v>9.6999999999999993</v>
       </c>
-      <c r="E164" s="4">
+      <c r="E164" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="F164" s="4">
         <v>71</v>
       </c>
-      <c r="H164" s="4">
+      <c r="I164" s="4">
         <v>1</v>
       </c>
-      <c r="I164" s="4">
-        <v>0</v>
-      </c>
       <c r="J164" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="165" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K164" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A165" s="10">
         <v>45383</v>
       </c>
@@ -4766,11 +5612,11 @@
       <c r="D165" s="12">
         <v>12.7</v>
       </c>
-      <c r="E165" s="4">
+      <c r="E165" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="F165" s="4">
         <v>63</v>
-      </c>
-      <c r="H165" s="4">
-        <v>1</v>
       </c>
       <c r="I165" s="4">
         <v>1</v>
@@ -4778,8 +5624,11 @@
       <c r="J165" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K165" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A166" s="10">
         <v>45413</v>
       </c>
@@ -4792,20 +5641,23 @@
       <c r="D166" s="12">
         <v>16.2</v>
       </c>
-      <c r="E166" s="4">
+      <c r="E166" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="F166" s="4">
         <v>68</v>
       </c>
-      <c r="H166" s="4">
-        <v>0</v>
-      </c>
       <c r="I166" s="4">
         <v>0</v>
       </c>
       <c r="J166" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="167" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K166" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A167" s="10">
         <v>45444</v>
       </c>
@@ -4818,20 +5670,23 @@
       <c r="D167" s="12">
         <v>21.2</v>
       </c>
-      <c r="E167" s="4">
+      <c r="E167" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="F167" s="4">
         <v>71</v>
       </c>
-      <c r="H167" s="4">
-        <v>0</v>
-      </c>
       <c r="I167" s="4">
         <v>0</v>
       </c>
       <c r="J167" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="168" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K167" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A168" s="10">
         <v>45474</v>
       </c>
@@ -4844,20 +5699,23 @@
       <c r="D168" s="12">
         <v>24.4</v>
       </c>
-      <c r="E168" s="4">
+      <c r="E168" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="F168" s="4">
         <v>68</v>
       </c>
-      <c r="H168" s="4">
-        <v>0</v>
-      </c>
       <c r="I168" s="4">
         <v>0</v>
       </c>
       <c r="J168" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="169" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K168" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A169" s="10">
         <v>45505</v>
       </c>
@@ -4870,20 +5728,23 @@
       <c r="D169" s="12">
         <v>24.4</v>
       </c>
-      <c r="E169" s="4">
+      <c r="E169" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="F169" s="4">
         <v>70</v>
       </c>
-      <c r="H169" s="4">
-        <v>0</v>
-      </c>
       <c r="I169" s="4">
         <v>0</v>
       </c>
       <c r="J169" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="170" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K169" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A170" s="10">
         <v>45536</v>
       </c>
@@ -4896,20 +5757,23 @@
       <c r="D170" s="12">
         <v>17.2</v>
       </c>
-      <c r="E170" s="4">
+      <c r="E170" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="F170" s="4">
         <v>76</v>
       </c>
-      <c r="H170" s="4">
-        <v>0</v>
-      </c>
       <c r="I170" s="4">
         <v>0</v>
       </c>
       <c r="J170" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="171" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K170" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A171" s="10">
         <v>45566</v>
       </c>
@@ -4922,20 +5786,23 @@
       <c r="D171" s="12">
         <v>13.2</v>
       </c>
-      <c r="E171" s="4">
+      <c r="E171" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="F171" s="4">
         <v>89</v>
       </c>
-      <c r="H171" s="4">
-        <v>0</v>
-      </c>
       <c r="I171" s="4">
         <v>0</v>
       </c>
       <c r="J171" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="172" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K171" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A172" s="10">
         <v>45597</v>
       </c>
@@ -4948,11 +5815,11 @@
       <c r="D172" s="12">
         <v>5.4</v>
       </c>
-      <c r="E172" s="4">
+      <c r="E172" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="F172" s="4">
         <v>89</v>
-      </c>
-      <c r="H172" s="4">
-        <v>2</v>
       </c>
       <c r="I172" s="4">
         <v>2</v>
@@ -4960,8 +5827,11 @@
       <c r="J172" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="173" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K172" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="173" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A173" s="10">
         <v>45627</v>
       </c>
@@ -4974,16 +5844,19 @@
       <c r="D173" s="12">
         <v>2</v>
       </c>
-      <c r="E173" s="4">
+      <c r="E173" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="F173" s="4">
         <v>88</v>
       </c>
-      <c r="H173" s="4">
+      <c r="I173" s="4">
         <v>1</v>
       </c>
-      <c r="I173" s="4">
+      <c r="J173" s="4">
         <v>2</v>
       </c>
-      <c r="J173" s="4">
+      <c r="K173" s="4">
         <v>6</v>
       </c>
     </row>
